--- a/template_preventivo.xlsx
+++ b/template_preventivo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maxporte.sharepoint.com/sites/MPCloud/Documenti condivisi/MPX/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18265FFA-220E-4D1E-B41E-5E68ECCFB06B}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{CC15ACFE-ED8D-4D36-8DB1-DE3148A82591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29137AAA-2EE4-49BE-A787-BFED7D4CDA33}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{2F1D62B1-3FD5-4D97-A455-0CD2ABF42920}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="PAGINA_FINALE" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">PAGINA_FINALE!$A$1:$AO$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">PAGINA_FINALE!$A$1:$AO$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PAGINE_INTERMEDIE!$A$1:$AO$49</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">PRIMA_PAGINA!$A$1:$AO$61</definedName>
     <definedName name="DATI_CLIENTE" localSheetId="2">PAGINA_FINALE!$A$18:$AO$28</definedName>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="223">
   <si>
     <t>TIPO DOCUMENTO</t>
   </si>
@@ -791,6 +791,12 @@
   <si>
     <t>*BANCA_DI_APPOGGIO*
 CIN *CIN* - ABI *ABI* - CAB *CAB*</t>
+  </si>
+  <si>
+    <t>ARROTONDAMENTO</t>
+  </si>
+  <si>
+    <t>*ARROTONDAMENTO*</t>
   </si>
 </sst>
 </file>
@@ -819,6 +825,7 @@
       <sz val="5"/>
       <color indexed="8"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1581,6 +1588,156 @@
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1588,156 +1745,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2145,28 +2152,28 @@
       <c r="S2" s="82"/>
       <c r="T2" s="82"/>
       <c r="U2" s="82"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="82"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
+      <c r="AB2" s="82"/>
+      <c r="AC2" s="82"/>
+      <c r="AD2" s="82"/>
+      <c r="AE2" s="82"/>
+      <c r="AF2" s="82"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="82"/>
+      <c r="AI2" s="82"/>
+      <c r="AJ2" s="82"/>
       <c r="AK2" s="1"/>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:41" ht="2.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" ht="2.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -2468,7 +2475,7 @@
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
     </row>
-    <row r="10" spans="1:41" ht="7" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" ht="6.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1"/>
       <c r="B10" s="102" t="s">
         <v>0</v>
@@ -3025,13 +3032,13 @@
       <c r="O21" s="59"/>
       <c r="P21" s="59"/>
       <c r="Q21" s="60"/>
-      <c r="R21" s="163" t="s">
+      <c r="R21" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="S21" s="164"/>
-      <c r="T21" s="164"/>
-      <c r="U21" s="164"/>
-      <c r="V21" s="165"/>
+      <c r="S21" s="114"/>
+      <c r="T21" s="114"/>
+      <c r="U21" s="114"/>
+      <c r="V21" s="115"/>
       <c r="W21" s="67" t="s">
         <v>67</v>
       </c>
@@ -5586,7 +5593,7 @@
     <mergeCell ref="Y5:AJ5"/>
     <mergeCell ref="Y6:AJ6"/>
     <mergeCell ref="Y7:AJ7"/>
-    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="J2:AJ2"/>
     <mergeCell ref="AJ18:AN18"/>
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="K19:Q19"/>
@@ -5864,7 +5871,7 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:41" ht="2.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" ht="2.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -8845,7 +8852,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AO69"/>
+  <dimension ref="A1:AO70"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="13.9" customHeight="1" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
@@ -8935,7 +8942,7 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:41" ht="2.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" ht="2.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -9787,13 +9794,13 @@
       <c r="J21" s="111"/>
       <c r="K21" s="111"/>
       <c r="L21" s="112"/>
-      <c r="M21" s="113" t="s">
+      <c r="M21" s="163" t="s">
         <v>32</v>
       </c>
-      <c r="N21" s="114"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="115"/>
+      <c r="N21" s="164"/>
+      <c r="O21" s="164"/>
+      <c r="P21" s="164"/>
+      <c r="Q21" s="165"/>
       <c r="R21" s="61" t="s">
         <v>31</v>
       </c>
@@ -10521,7 +10528,7 @@
       <c r="U37" s="39"/>
       <c r="V37" s="39"/>
       <c r="AA37" s="149" t="s">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="AB37" s="150"/>
       <c r="AC37" s="150"/>
@@ -10535,7 +10542,7 @@
       </c>
       <c r="AJ37" s="151"/>
       <c r="AK37" s="151" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="AL37" s="151"/>
       <c r="AM37" s="151"/>
@@ -10565,7 +10572,7 @@
       <c r="U38" s="39"/>
       <c r="V38" s="39"/>
       <c r="AA38" s="149" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AB38" s="150"/>
       <c r="AC38" s="150"/>
@@ -10579,7 +10586,7 @@
       </c>
       <c r="AJ38" s="151"/>
       <c r="AK38" s="151" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
       <c r="AL38" s="151"/>
       <c r="AM38" s="151"/>
@@ -10609,7 +10616,7 @@
       <c r="U39" s="39"/>
       <c r="V39" s="39"/>
       <c r="AA39" s="149" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="AB39" s="150"/>
       <c r="AC39" s="150"/>
@@ -10623,7 +10630,7 @@
       </c>
       <c r="AJ39" s="151"/>
       <c r="AK39" s="151" t="s">
-        <v>185</v>
+        <v>61</v>
       </c>
       <c r="AL39" s="151"/>
       <c r="AM39" s="151"/>
@@ -10653,7 +10660,7 @@
       <c r="U40" s="39"/>
       <c r="V40" s="39"/>
       <c r="AA40" s="149" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB40" s="150"/>
       <c r="AC40" s="150"/>
@@ -10667,7 +10674,7 @@
       </c>
       <c r="AJ40" s="151"/>
       <c r="AK40" s="151" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AL40" s="151"/>
       <c r="AM40" s="151"/>
@@ -10697,7 +10704,7 @@
       <c r="U41" s="39"/>
       <c r="V41" s="39"/>
       <c r="AA41" s="149" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="AB41" s="150"/>
       <c r="AC41" s="150"/>
@@ -10711,13 +10718,13 @@
       </c>
       <c r="AJ41" s="151"/>
       <c r="AK41" s="151" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AL41" s="151"/>
       <c r="AM41" s="151"/>
       <c r="AN41" s="155"/>
     </row>
-    <row r="42" spans="1:41" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1"/>
       <c r="B42" s="32"/>
       <c r="C42" s="32"/>
@@ -10740,34 +10747,34 @@
       <c r="T42" s="39"/>
       <c r="U42" s="39"/>
       <c r="V42" s="39"/>
-      <c r="AA42" s="153" t="s">
-        <v>177</v>
-      </c>
-      <c r="AB42" s="154"/>
-      <c r="AC42" s="154"/>
-      <c r="AD42" s="154"/>
-      <c r="AE42" s="154"/>
-      <c r="AF42" s="154"/>
-      <c r="AG42" s="154"/>
-      <c r="AH42" s="154"/>
-      <c r="AI42" s="152" t="s">
+      <c r="AA42" s="149" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB42" s="150"/>
+      <c r="AC42" s="150"/>
+      <c r="AD42" s="150"/>
+      <c r="AE42" s="150"/>
+      <c r="AF42" s="150"/>
+      <c r="AG42" s="150"/>
+      <c r="AH42" s="150"/>
+      <c r="AI42" s="151" t="s">
         <v>168</v>
       </c>
-      <c r="AJ42" s="152"/>
-      <c r="AK42" s="152" t="s">
-        <v>188</v>
-      </c>
-      <c r="AL42" s="152"/>
-      <c r="AM42" s="152"/>
-      <c r="AN42" s="162"/>
-    </row>
-    <row r="43" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AJ42" s="151"/>
+      <c r="AK42" s="151" t="s">
+        <v>187</v>
+      </c>
+      <c r="AL42" s="151"/>
+      <c r="AM42" s="151"/>
+      <c r="AN42" s="155"/>
+    </row>
+    <row r="43" spans="1:41" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1"/>
       <c r="B43" s="32"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
       <c r="G43" s="34"/>
       <c r="H43" s="31"/>
       <c r="I43" s="31"/>
@@ -10784,74 +10791,75 @@
       <c r="T43" s="39"/>
       <c r="U43" s="39"/>
       <c r="V43" s="39"/>
-      <c r="W43" s="39"/>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="39"/>
-      <c r="Z43" s="39"/>
-      <c r="AA43" s="20"/>
-      <c r="AB43" s="40"/>
-      <c r="AC43" s="40"/>
-      <c r="AD43" s="40"/>
-      <c r="AE43" s="40"/>
-      <c r="AF43" s="40"/>
-      <c r="AG43" s="43"/>
-      <c r="AH43" s="43"/>
-      <c r="AI43" s="43"/>
-      <c r="AJ43" s="43"/>
-      <c r="AK43" s="43"/>
-      <c r="AL43" s="43"/>
-      <c r="AM43" s="43"/>
-      <c r="AN43" s="43"/>
-      <c r="AO43" s="13"/>
+      <c r="AA43" s="153" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB43" s="154"/>
+      <c r="AC43" s="154"/>
+      <c r="AD43" s="154"/>
+      <c r="AE43" s="154"/>
+      <c r="AF43" s="154"/>
+      <c r="AG43" s="154"/>
+      <c r="AH43" s="154"/>
+      <c r="AI43" s="152" t="s">
+        <v>168</v>
+      </c>
+      <c r="AJ43" s="152"/>
+      <c r="AK43" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL43" s="152"/>
+      <c r="AM43" s="152"/>
+      <c r="AN43" s="162"/>
     </row>
     <row r="44" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1"/>
-      <c r="B44" s="146" t="s">
-        <v>178</v>
-      </c>
-      <c r="C44" s="146"/>
-      <c r="D44" s="146"/>
-      <c r="E44" s="146"/>
-      <c r="F44" s="146"/>
-      <c r="G44" s="146"/>
-      <c r="H44" s="146"/>
-      <c r="I44" s="146"/>
-      <c r="J44" s="146"/>
-      <c r="K44" s="146"/>
-      <c r="L44" s="146"/>
-      <c r="M44" s="146"/>
-      <c r="N44" s="146"/>
-      <c r="O44" s="146"/>
-      <c r="P44" s="146"/>
-      <c r="Q44" s="146"/>
-      <c r="R44" s="146"/>
-      <c r="S44" s="146"/>
-      <c r="T44" s="146"/>
-      <c r="U44" s="146"/>
-      <c r="V44" s="146"/>
-      <c r="W44" s="146"/>
-      <c r="X44" s="146"/>
-      <c r="Y44" s="146"/>
-      <c r="Z44" s="146"/>
-      <c r="AA44" s="146"/>
-      <c r="AB44" s="146"/>
-      <c r="AC44" s="146"/>
-      <c r="AD44" s="146"/>
-      <c r="AE44" s="146"/>
-      <c r="AF44" s="146"/>
-      <c r="AG44" s="146"/>
-      <c r="AH44" s="146"/>
-      <c r="AI44" s="146"/>
-      <c r="AJ44" s="146"/>
-      <c r="AK44" s="146"/>
-      <c r="AL44" s="146"/>
-      <c r="AM44" s="146"/>
-      <c r="AN44" s="146"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="31"/>
+      <c r="M44" s="31"/>
+      <c r="N44" s="31"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="39"/>
+      <c r="Q44" s="39"/>
+      <c r="R44" s="39"/>
+      <c r="S44" s="39"/>
+      <c r="T44" s="39"/>
+      <c r="U44" s="39"/>
+      <c r="V44" s="39"/>
+      <c r="W44" s="39"/>
+      <c r="X44" s="39"/>
+      <c r="Y44" s="39"/>
+      <c r="Z44" s="39"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="40"/>
+      <c r="AC44" s="40"/>
+      <c r="AD44" s="40"/>
+      <c r="AE44" s="40"/>
+      <c r="AF44" s="40"/>
+      <c r="AG44" s="43"/>
+      <c r="AH44" s="43"/>
+      <c r="AI44" s="43"/>
+      <c r="AJ44" s="43"/>
+      <c r="AK44" s="43"/>
+      <c r="AL44" s="43"/>
+      <c r="AM44" s="43"/>
+      <c r="AN44" s="43"/>
       <c r="AO44" s="13"/>
     </row>
     <row r="45" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1"/>
-      <c r="B45" s="146"/>
+      <c r="B45" s="146" t="s">
+        <v>178</v>
+      </c>
       <c r="C45" s="146"/>
       <c r="D45" s="146"/>
       <c r="E45" s="146"/>
@@ -11449,6 +11457,7 @@
       <c r="AL58" s="146"/>
       <c r="AM58" s="146"/>
       <c r="AN58" s="146"/>
+      <c r="AO58" s="13"/>
     </row>
     <row r="59" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1"/>
@@ -11491,50 +11500,49 @@
       <c r="AL59" s="146"/>
       <c r="AM59" s="146"/>
       <c r="AN59" s="146"/>
-      <c r="AO59" s="13"/>
     </row>
     <row r="60" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
-      <c r="N60" s="18"/>
-      <c r="O60" s="18"/>
-      <c r="P60" s="18"/>
-      <c r="Q60" s="18"/>
-      <c r="R60" s="18"/>
-      <c r="S60" s="18"/>
-      <c r="T60" s="18"/>
-      <c r="U60" s="18"/>
-      <c r="V60" s="18"/>
-      <c r="W60" s="18"/>
-      <c r="X60" s="18"/>
-      <c r="Y60" s="18"/>
-      <c r="Z60" s="18"/>
-      <c r="AA60" s="18"/>
-      <c r="AB60" s="18"/>
-      <c r="AC60" s="18"/>
-      <c r="AD60" s="18"/>
-      <c r="AE60" s="18"/>
-      <c r="AF60" s="18"/>
-      <c r="AG60" s="18"/>
-      <c r="AH60" s="18"/>
-      <c r="AI60" s="18"/>
-      <c r="AJ60" s="18"/>
-      <c r="AK60" s="18"/>
-      <c r="AL60" s="18"/>
-      <c r="AM60" s="18"/>
-      <c r="AN60" s="18"/>
-      <c r="AO60" s="18"/>
+      <c r="B60" s="146"/>
+      <c r="C60" s="146"/>
+      <c r="D60" s="146"/>
+      <c r="E60" s="146"/>
+      <c r="F60" s="146"/>
+      <c r="G60" s="146"/>
+      <c r="H60" s="146"/>
+      <c r="I60" s="146"/>
+      <c r="J60" s="146"/>
+      <c r="K60" s="146"/>
+      <c r="L60" s="146"/>
+      <c r="M60" s="146"/>
+      <c r="N60" s="146"/>
+      <c r="O60" s="146"/>
+      <c r="P60" s="146"/>
+      <c r="Q60" s="146"/>
+      <c r="R60" s="146"/>
+      <c r="S60" s="146"/>
+      <c r="T60" s="146"/>
+      <c r="U60" s="146"/>
+      <c r="V60" s="146"/>
+      <c r="W60" s="146"/>
+      <c r="X60" s="146"/>
+      <c r="Y60" s="146"/>
+      <c r="Z60" s="146"/>
+      <c r="AA60" s="146"/>
+      <c r="AB60" s="146"/>
+      <c r="AC60" s="146"/>
+      <c r="AD60" s="146"/>
+      <c r="AE60" s="146"/>
+      <c r="AF60" s="146"/>
+      <c r="AG60" s="146"/>
+      <c r="AH60" s="146"/>
+      <c r="AI60" s="146"/>
+      <c r="AJ60" s="146"/>
+      <c r="AK60" s="146"/>
+      <c r="AL60" s="146"/>
+      <c r="AM60" s="146"/>
+      <c r="AN60" s="146"/>
+      <c r="AO60" s="13"/>
     </row>
     <row r="61" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1"/>
@@ -11577,6 +11585,7 @@
       <c r="AL61" s="18"/>
       <c r="AM61" s="18"/>
       <c r="AN61" s="18"/>
+      <c r="AO61" s="18"/>
     </row>
     <row r="62" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1"/>
@@ -11706,88 +11715,87 @@
     </row>
     <row r="65" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="19"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
-      <c r="L65" s="19"/>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
-      <c r="S65" s="19"/>
-      <c r="T65" s="19"/>
-      <c r="U65" s="19"/>
-      <c r="V65" s="19"/>
-      <c r="W65" s="19"/>
-      <c r="X65" s="19"/>
-      <c r="Y65" s="19"/>
-      <c r="Z65" s="19"/>
-      <c r="AA65" s="19"/>
-      <c r="AB65" s="19"/>
-      <c r="AC65" s="19"/>
-      <c r="AD65" s="19"/>
-      <c r="AE65" s="19"/>
-      <c r="AF65" s="19"/>
-      <c r="AG65" s="19"/>
-      <c r="AH65" s="19"/>
-      <c r="AI65" s="19"/>
-      <c r="AJ65" s="19"/>
-      <c r="AK65" s="19"/>
-      <c r="AL65" s="143"/>
-      <c r="AM65" s="143"/>
-      <c r="AN65" s="143"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
+      <c r="R65" s="18"/>
+      <c r="S65" s="18"/>
+      <c r="T65" s="18"/>
+      <c r="U65" s="18"/>
+      <c r="V65" s="18"/>
+      <c r="W65" s="18"/>
+      <c r="X65" s="18"/>
+      <c r="Y65" s="18"/>
+      <c r="Z65" s="18"/>
+      <c r="AA65" s="18"/>
+      <c r="AB65" s="18"/>
+      <c r="AC65" s="18"/>
+      <c r="AD65" s="18"/>
+      <c r="AE65" s="18"/>
+      <c r="AF65" s="18"/>
+      <c r="AG65" s="18"/>
+      <c r="AH65" s="18"/>
+      <c r="AI65" s="18"/>
+      <c r="AJ65" s="18"/>
+      <c r="AK65" s="18"/>
+      <c r="AL65" s="18"/>
+      <c r="AM65" s="18"/>
+      <c r="AN65" s="18"/>
     </row>
     <row r="66" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
-      <c r="U66" s="5"/>
-      <c r="V66" s="5"/>
-      <c r="W66" s="5"/>
-      <c r="X66" s="5"/>
-      <c r="Y66" s="5"/>
-      <c r="Z66" s="5"/>
-      <c r="AA66" s="5"/>
-      <c r="AB66" s="5"/>
-      <c r="AC66" s="5"/>
-      <c r="AD66" s="5"/>
-      <c r="AE66" s="5"/>
-      <c r="AF66" s="5"/>
-      <c r="AG66" s="5"/>
-      <c r="AH66" s="5"/>
-      <c r="AI66" s="5"/>
-      <c r="AJ66" s="5"/>
-      <c r="AK66" s="5"/>
-      <c r="AL66" s="5"/>
-      <c r="AM66" s="5"/>
-      <c r="AN66" s="5"/>
-      <c r="AO66" s="5"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="19"/>
+      <c r="Q66" s="19"/>
+      <c r="R66" s="19"/>
+      <c r="S66" s="19"/>
+      <c r="T66" s="19"/>
+      <c r="U66" s="19"/>
+      <c r="V66" s="19"/>
+      <c r="W66" s="19"/>
+      <c r="X66" s="19"/>
+      <c r="Y66" s="19"/>
+      <c r="Z66" s="19"/>
+      <c r="AA66" s="19"/>
+      <c r="AB66" s="19"/>
+      <c r="AC66" s="19"/>
+      <c r="AD66" s="19"/>
+      <c r="AE66" s="19"/>
+      <c r="AF66" s="19"/>
+      <c r="AG66" s="19"/>
+      <c r="AH66" s="19"/>
+      <c r="AI66" s="19"/>
+      <c r="AJ66" s="19"/>
+      <c r="AK66" s="19"/>
+      <c r="AL66" s="143"/>
+      <c r="AM66" s="143"/>
+      <c r="AN66" s="143"/>
     </row>
     <row r="67" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1"/>
@@ -11822,11 +11830,11 @@
       <c r="AD67" s="5"/>
       <c r="AE67" s="5"/>
       <c r="AF67" s="5"/>
-      <c r="AG67" s="15"/>
-      <c r="AH67" s="15"/>
-      <c r="AI67" s="15"/>
-      <c r="AJ67" s="15"/>
-      <c r="AK67" s="15"/>
+      <c r="AG67" s="5"/>
+      <c r="AH67" s="5"/>
+      <c r="AI67" s="5"/>
+      <c r="AJ67" s="5"/>
+      <c r="AK67" s="5"/>
       <c r="AL67" s="5"/>
       <c r="AM67" s="5"/>
       <c r="AN67" s="5"/>
@@ -11908,18 +11916,61 @@
       <c r="AD69" s="5"/>
       <c r="AE69" s="5"/>
       <c r="AF69" s="5"/>
-      <c r="AG69" s="5"/>
-      <c r="AH69" s="5"/>
-      <c r="AI69" s="5"/>
-      <c r="AJ69" s="5"/>
-      <c r="AK69" s="5"/>
+      <c r="AG69" s="15"/>
+      <c r="AH69" s="15"/>
+      <c r="AI69" s="15"/>
+      <c r="AJ69" s="15"/>
+      <c r="AK69" s="15"/>
       <c r="AL69" s="5"/>
       <c r="AM69" s="5"/>
       <c r="AN69" s="5"/>
       <c r="AO69" s="5"/>
     </row>
+    <row r="70" spans="1:41" ht="13.9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="1"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="5"/>
+      <c r="R70" s="5"/>
+      <c r="S70" s="5"/>
+      <c r="T70" s="5"/>
+      <c r="U70" s="5"/>
+      <c r="V70" s="5"/>
+      <c r="W70" s="5"/>
+      <c r="X70" s="5"/>
+      <c r="Y70" s="5"/>
+      <c r="Z70" s="5"/>
+      <c r="AA70" s="5"/>
+      <c r="AB70" s="5"/>
+      <c r="AC70" s="5"/>
+      <c r="AD70" s="5"/>
+      <c r="AE70" s="5"/>
+      <c r="AF70" s="5"/>
+      <c r="AG70" s="5"/>
+      <c r="AH70" s="5"/>
+      <c r="AI70" s="5"/>
+      <c r="AJ70" s="5"/>
+      <c r="AK70" s="5"/>
+      <c r="AL70" s="5"/>
+      <c r="AM70" s="5"/>
+      <c r="AN70" s="5"/>
+      <c r="AO70" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="96">
+  <mergeCells count="99">
     <mergeCell ref="J6:U6"/>
     <mergeCell ref="Y6:AJ6"/>
     <mergeCell ref="J2:U2"/>
@@ -11980,18 +12031,20 @@
     <mergeCell ref="L23:W24"/>
     <mergeCell ref="X23:AC23"/>
     <mergeCell ref="X24:AC24"/>
-    <mergeCell ref="AL65:AN65"/>
+    <mergeCell ref="AL66:AN66"/>
+    <mergeCell ref="AI40:AJ40"/>
     <mergeCell ref="AI39:AJ39"/>
     <mergeCell ref="AI38:AJ38"/>
+    <mergeCell ref="AI36:AJ36"/>
     <mergeCell ref="AI37:AJ37"/>
-    <mergeCell ref="AI36:AJ36"/>
+    <mergeCell ref="AK37:AN37"/>
     <mergeCell ref="AA30:AN31"/>
+    <mergeCell ref="AK43:AN43"/>
     <mergeCell ref="AK42:AN42"/>
     <mergeCell ref="AK41:AN41"/>
     <mergeCell ref="AK40:AN40"/>
     <mergeCell ref="AK39:AN39"/>
     <mergeCell ref="AK38:AN38"/>
-    <mergeCell ref="AK37:AN37"/>
     <mergeCell ref="AK36:AN36"/>
     <mergeCell ref="AK35:AN35"/>
     <mergeCell ref="AK34:AN34"/>
@@ -12002,20 +12055,21 @@
     <mergeCell ref="AI35:AJ35"/>
     <mergeCell ref="AA33:AH33"/>
     <mergeCell ref="AA32:AH32"/>
-    <mergeCell ref="B44:AN59"/>
+    <mergeCell ref="B45:AN60"/>
+    <mergeCell ref="AA40:AH40"/>
     <mergeCell ref="AA39:AH39"/>
     <mergeCell ref="AA38:AH38"/>
-    <mergeCell ref="AA37:AH37"/>
     <mergeCell ref="AA36:AH36"/>
     <mergeCell ref="AA35:AH35"/>
     <mergeCell ref="AA34:AH34"/>
-    <mergeCell ref="AI40:AJ40"/>
     <mergeCell ref="AI41:AJ41"/>
     <mergeCell ref="AI42:AJ42"/>
+    <mergeCell ref="AI43:AJ43"/>
+    <mergeCell ref="AA43:AH43"/>
     <mergeCell ref="AA42:AH42"/>
     <mergeCell ref="AA41:AH41"/>
-    <mergeCell ref="AA40:AH40"/>
     <mergeCell ref="AK33:AN33"/>
+    <mergeCell ref="AA37:AH37"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -12026,6 +12080,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009C338B9B438D674598E8DA2C9D466197" ma:contentTypeVersion="12" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="bbbbe07d582d2b880b9f84f421d4cf93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="13b50d63-4097-4260-987b-0df3cda3515c" xmlns:ns3="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7711d34beda0080ad730e76db80bbe12" ns2:_="" ns3:_="">
     <xsd:import namespace="13b50d63-4097-4260-987b-0df3cda3515c"/>
@@ -12226,27 +12300,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bdc2d3d5-fc31-4d65-8e89-042f9aabae79" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="13b50d63-4097-4260-987b-0df3cda3515c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
+    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84E6239E-971F-4DA0-B0B2-60403B8393FE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12263,23 +12336,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED9081D4-7DA8-4E8C-9299-427A52260533}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA865533-0B77-4147-AA92-F0C2FDB2E315}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bdc2d3d5-fc31-4d65-8e89-042f9aabae79"/>
-    <ds:schemaRef ds:uri="13b50d63-4097-4260-987b-0df3cda3515c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>